--- a/1-LATEX/2-DADOS/3-OUTPUT/diagnostico_evidencia_mista.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/diagnostico_evidencia_mista.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -519,40 +519,40 @@
         <v>37</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="D3">
-        <v>0.04486936865938158</v>
+        <v>0.03963900211143596</v>
       </c>
       <c r="E3">
-        <v>0.05067840210943259</v>
+        <v>0.04296894678024794</v>
       </c>
       <c r="F3">
-        <v>-0.06699133405373206</v>
+        <v>-0.05421778088792478</v>
       </c>
       <c r="G3">
-        <v>0.1567300713724952</v>
+        <v>0.1334957851107967</v>
       </c>
       <c r="H3">
-        <v>-0.2573821296484547</v>
+        <v>-0.2435464867858387</v>
       </c>
       <c r="I3">
-        <v>0.3471208669672178</v>
+        <v>0.3228244910087106</v>
       </c>
       <c r="J3">
-        <v>0.02121684597796045</v>
+        <v>0.01903144035028564</v>
       </c>
       <c r="K3">
-        <v>2.438881119435557</v>
+        <v>2.922284588274979</v>
       </c>
       <c r="L3">
-        <v>71.56436801653555</v>
+        <v>133.3786086672545</v>
       </c>
       <c r="M3">
-        <v>0.0003834809409339813</v>
+        <v>2.072438079405914E-05</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="P3">
-        <v>4.589122481166008</v>
+        <v>4.043511151130708</v>
       </c>
       <c r="Q3">
-        <v>-6.479669427674262</v>
+        <v>-5.2774203637586</v>
       </c>
       <c r="R3">
-        <v>16.96798412106284</v>
+        <v>14.28164492802446</v>
       </c>
     </row>
     <row r="4">
@@ -582,34 +582,34 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>0.0715762333435533</v>
+        <v>0.007406689764050332</v>
       </c>
       <c r="E4">
-        <v>0.07407978426217285</v>
+        <v>0.1024738071765175</v>
       </c>
       <c r="F4">
-        <v>-0.08972584687221617</v>
+        <v>-0.209830231702959</v>
       </c>
       <c r="G4">
-        <v>0.2328783135593228</v>
+        <v>0.2246436112310597</v>
       </c>
       <c r="H4">
-        <v>-0.2849219257603118</v>
+        <v>-0.6215924440755325</v>
       </c>
       <c r="I4">
-        <v>0.4280743924474184</v>
+        <v>0.6364058236036332</v>
       </c>
       <c r="J4">
-        <v>0.02766083365694542</v>
+        <v>0.09260327465570292</v>
       </c>
       <c r="K4">
-        <v>6.074724192460008</v>
+        <v>7.6296542198637</v>
       </c>
       <c r="L4">
-        <v>26.26739414566603</v>
+        <v>37.43656165331915</v>
       </c>
       <c r="M4">
-        <v>0.8829643996734775</v>
+        <v>0.4030297403812922</v>
       </c>
       <c r="N4">
         <v>2</v>
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="P4">
-        <v>7.420003744052339</v>
+        <v>0.7434187136927894</v>
       </c>
       <c r="Q4">
-        <v>-8.581822328710631</v>
+        <v>-18.92781308410697</v>
       </c>
       <c r="R4">
-        <v>26.22278739642996</v>
+        <v>25.1876481961882</v>
       </c>
     </row>
     <row r="5">
@@ -642,37 +642,37 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>0.007406689764050332</v>
+        <v>-0.2787297834856938</v>
       </c>
       <c r="E5">
-        <v>0.1024738071765175</v>
+        <v>0.1053211656521511</v>
       </c>
       <c r="F5">
-        <v>-0.209830231702959</v>
+        <v>-0.4940231495961557</v>
       </c>
       <c r="G5">
-        <v>0.2246436112310597</v>
+        <v>-0.06343641737523192</v>
       </c>
       <c r="H5">
-        <v>-0.6215924440755325</v>
+        <v>-1.113866715587769</v>
       </c>
       <c r="I5">
-        <v>0.6364058236036332</v>
+        <v>0.5564071486163809</v>
       </c>
       <c r="J5">
-        <v>0.09260327465570292</v>
+        <v>0.1706084964705022</v>
       </c>
       <c r="K5">
-        <v>7.6296542198637</v>
+        <v>30.6884426347705</v>
       </c>
       <c r="L5">
-        <v>37.43656165331915</v>
+        <v>125.9213409842246</v>
       </c>
       <c r="M5">
-        <v>0.4030297403812922</v>
+        <v>6.653162462603374E-12</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -680,13 +680,13 @@
         </is>
       </c>
       <c r="P5">
-        <v>0.7434187136927894</v>
+        <v>-24.32556395867607</v>
       </c>
       <c r="Q5">
-        <v>-18.92781308410697</v>
+        <v>-38.98333421845329</v>
       </c>
       <c r="R5">
-        <v>25.1876481961882</v>
+        <v>-6.146620815450554</v>
       </c>
     </row>
     <row r="6">
@@ -702,34 +702,34 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>-0.2787297834856938</v>
+        <v>0.1716000516462755</v>
       </c>
       <c r="E6">
-        <v>0.1053211656521511</v>
+        <v>0.1058399698659169</v>
       </c>
       <c r="F6">
-        <v>-0.4940231495961557</v>
+        <v>-0.05482597278044252</v>
       </c>
       <c r="G6">
-        <v>-0.06343641737523192</v>
+        <v>0.3980260760729936</v>
       </c>
       <c r="H6">
-        <v>-1.113866715587769</v>
+        <v>-0.4852238459102494</v>
       </c>
       <c r="I6">
-        <v>0.5564071486163809</v>
+        <v>0.8284239492028005</v>
       </c>
       <c r="J6">
-        <v>0.1706084964705022</v>
+        <v>0.1011508222168174</v>
       </c>
       <c r="K6">
-        <v>30.6884426347705</v>
+        <v>8.402530217900857</v>
       </c>
       <c r="L6">
-        <v>125.9213409842246</v>
+        <v>46.24359044734757</v>
       </c>
       <c r="M6">
-        <v>6.653162462603374E-12</v>
+        <v>0.1178926285696138</v>
       </c>
       <c r="N6">
         <v>3</v>
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="P6">
-        <v>-24.32556395867607</v>
+        <v>18.72029183967872</v>
       </c>
       <c r="Q6">
-        <v>-38.98333421845329</v>
+        <v>-5.335012353465862</v>
       </c>
       <c r="R6">
-        <v>-6.146620815450554</v>
+        <v>48.88828536190604</v>
       </c>
     </row>
     <row r="7">
@@ -756,43 +756,43 @@
         </is>
       </c>
       <c r="B7">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>0.1716000516462755</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0.1058399698659169</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>-0.05482597278044252</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0.3980260760729936</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>-0.4852238459102494</v>
+        <v>-0.7100502051691578</v>
       </c>
       <c r="I7">
-        <v>0.8284239492028005</v>
+        <v>0.7100502051691578</v>
       </c>
       <c r="J7">
-        <v>0.1011508222168174</v>
+        <v>2.991635273407584E-09</v>
       </c>
       <c r="K7">
-        <v>8.402530217900857</v>
+        <v>4.849856232471125E-08</v>
       </c>
       <c r="L7">
-        <v>46.24359044734757</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>0.1178926285696138</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -800,13 +800,133 @@
         </is>
       </c>
       <c r="P7">
-        <v>18.72029183967872</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>-5.335012353465862</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>48.88828536190604</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <v>47</v>
+      </c>
+      <c r="D8">
+        <v>0.05120757691971695</v>
+      </c>
+      <c r="E8">
+        <v>0.02863133275493802</v>
+      </c>
+      <c r="F8">
+        <v>-0.008771158994193597</v>
+      </c>
+      <c r="G8">
+        <v>0.1111863128336275</v>
+      </c>
+      <c r="H8">
+        <v>-0.5596308859050975</v>
+      </c>
+      <c r="I8">
+        <v>0.6620460397445315</v>
+      </c>
+      <c r="J8">
+        <v>2.049959082822693E-09</v>
+      </c>
+      <c r="K8">
+        <v>3.484681674090851E-08</v>
+      </c>
+      <c r="L8">
+        <v>0.0691238844262049</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Confirmatória (meta-análise completa)</t>
+        </is>
+      </c>
+      <c r="P8">
+        <v>5.254135390084591</v>
+      </c>
+      <c r="Q8">
+        <v>-0.8732804598560295</v>
+      </c>
+      <c r="R8">
+        <v>11.76031112608094</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>47</v>
+      </c>
+      <c r="C9">
+        <v>47</v>
+      </c>
+      <c r="D9">
+        <v>0.2796759127138764</v>
+      </c>
+      <c r="E9">
+        <v>0.06830923323750851</v>
+      </c>
+      <c r="F9">
+        <v>0.03385813408037175</v>
+      </c>
+      <c r="G9">
+        <v>0.525493691347381</v>
+      </c>
+      <c r="H9">
+        <v>0.04126572792222716</v>
+      </c>
+      <c r="I9">
+        <v>0.5180860975055256</v>
+      </c>
+      <c r="J9">
+        <v>4.631119017095811E-10</v>
+      </c>
+      <c r="K9">
+        <v>9.044973460047649E-09</v>
+      </c>
+      <c r="L9">
+        <v>2.306511664550499</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Confirmatória (meta-análise completa)</t>
+        </is>
+      </c>
+      <c r="P9">
+        <v>32.27010722657231</v>
+      </c>
+      <c r="Q9">
+        <v>3.443784484195223</v>
+      </c>
+      <c r="R9">
+        <v>69.12936193282822</v>
       </c>
     </row>
   </sheetData>
@@ -816,7 +936,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -875,13 +995,13 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>0.05538273110889344</v>
+        <v>0.1066540142239678</v>
       </c>
       <c r="D3">
-        <v>0.04486936865938158</v>
+        <v>0.03963900211143596</v>
       </c>
       <c r="E3">
-        <v>0.01051336244951186</v>
+        <v>0.06701501211253189</v>
       </c>
     </row>
     <row r="4">
@@ -894,13 +1014,13 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>0.2401404624100854</v>
+        <v>0.1000699399382928</v>
       </c>
       <c r="D4">
-        <v>0.0715762333435533</v>
+        <v>0.007406689764050332</v>
       </c>
       <c r="E4">
-        <v>0.1685642290665321</v>
+        <v>0.09266325017424248</v>
       </c>
     </row>
     <row r="5">
@@ -910,16 +1030,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>0.1000699399382928</v>
+        <v>0.4193334963587222</v>
       </c>
       <c r="D5">
-        <v>0.007406689764050332</v>
+        <v>-0.2787297834856938</v>
       </c>
       <c r="E5">
-        <v>0.09266325017424248</v>
+        <v>0.6980632798444161</v>
       </c>
     </row>
     <row r="6">
@@ -932,13 +1052,13 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>0.4193334963587222</v>
+        <v>0.555779164827344</v>
       </c>
       <c r="D6">
-        <v>-0.2787297834856938</v>
+        <v>0.1716000516462755</v>
       </c>
       <c r="E6">
-        <v>0.6980632798444161</v>
+        <v>0.3841791131810685</v>
       </c>
     </row>
     <row r="7">
@@ -947,17 +1067,19 @@
           <t>V6</t>
         </is>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>0.555779164827344</v>
-      </c>
-      <c r="D7">
-        <v>0.1716000516462755</v>
-      </c>
-      <c r="E7">
-        <v>0.3841791131810685</v>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -967,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1018,10 +1140,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.04486936865938158</v>
+        <v>0.04017651731205293</v>
       </c>
       <c r="D3">
-        <v>0.02121684597796045</v>
+        <v>0.01883838484902827</v>
       </c>
     </row>
     <row r="4">
@@ -1034,10 +1156,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.0715762333435533</v>
+        <v>0.007406689764050332</v>
       </c>
       <c r="D4">
-        <v>0.02766083365694542</v>
+        <v>0.09260327465570292</v>
       </c>
     </row>
     <row r="5">
@@ -1050,10 +1172,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.007406689764050332</v>
+        <v>-0.2787297834856938</v>
       </c>
       <c r="D5">
-        <v>0.09260327465570292</v>
+        <v>0.1706084964705022</v>
       </c>
     </row>
     <row r="6">
@@ -1066,10 +1188,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.2787297834856938</v>
+        <v>0.1716000516462755</v>
       </c>
       <c r="D6">
-        <v>0.1706084964705022</v>
+        <v>0.1011508222168174</v>
       </c>
     </row>
     <row r="7">
@@ -1082,42 +1204,42 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.1716000516462755</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0.1011508222168174</v>
+        <v>2.991635273407584E-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>V7</t>
         </is>
       </c>
       <c r="C8">
-        <v>-0.01702358794206319</v>
+        <v>0.05120757691971695</v>
       </c>
       <c r="D8">
-        <v>0.1692918142082444</v>
+        <v>2.049959082822693E-09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C9">
-        <v>0.04486936865938158</v>
+        <v>0.2796759127138764</v>
       </c>
       <c r="D9">
-        <v>0.02121684597796045</v>
+        <v>4.631119017095811E-10</v>
       </c>
     </row>
     <row r="10">
@@ -1126,14 +1248,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="C10">
-        <v>0.0715762333435533</v>
+        <v>-0.01702358794206319</v>
       </c>
       <c r="D10">
-        <v>0.02766083365694542</v>
+        <v>0.1692918142082444</v>
       </c>
     </row>
     <row r="11">
@@ -1142,14 +1264,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="C11">
-        <v>0.007406689764050332</v>
+        <v>0.03963900211143596</v>
       </c>
       <c r="D11">
-        <v>0.09260327465570292</v>
+        <v>0.01903144035028564</v>
       </c>
     </row>
     <row r="12">
@@ -1158,14 +1280,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="C12">
-        <v>-0.2787297834856938</v>
+        <v>0.007406689764050332</v>
       </c>
       <c r="D12">
-        <v>0.1706084964705022</v>
+        <v>0.09260327465570292</v>
       </c>
     </row>
     <row r="13">
@@ -1174,78 +1296,78 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V4</t>
         </is>
       </c>
       <c r="C13">
-        <v>0.1716000516462755</v>
+        <v>-0.2787297834856938</v>
       </c>
       <c r="D13">
-        <v>0.1011508222168174</v>
+        <v>0.1706084964705022</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>V5</t>
         </is>
       </c>
       <c r="C14">
-        <v>-0.01702358794206319</v>
+        <v>0.1716000516462755</v>
       </c>
       <c r="D14">
-        <v>0.1692918142082444</v>
+        <v>0.1011508222168174</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V6</t>
         </is>
       </c>
       <c r="C15">
-        <v>0.04486936865938158</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>0.02121684597796045</v>
+        <v>2.991635273407584E-09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>V7</t>
         </is>
       </c>
       <c r="C16">
-        <v>0.0715762333435533</v>
+        <v>0.05120757691971695</v>
       </c>
       <c r="D16">
-        <v>0.02766083365694542</v>
+        <v>2.049959082822693E-09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C17">
-        <v>0.007406689764050332</v>
+        <v>0.2796759127138764</v>
       </c>
       <c r="D17">
-        <v>0.09260327465570292</v>
+        <v>4.631119017095811E-10</v>
       </c>
     </row>
     <row r="18">
@@ -1254,14 +1376,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="C18">
-        <v>-0.2787297834856938</v>
+        <v>-0.01702358794206319</v>
       </c>
       <c r="D18">
-        <v>0.1706084964705022</v>
+        <v>0.1692918142082444</v>
       </c>
     </row>
     <row r="19">
@@ -1270,14 +1392,110 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>0.01655094290335919</v>
+      </c>
+      <c r="D19">
+        <v>0.02389601705864313</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.8</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>0.007406689764050332</v>
+      </c>
+      <c r="D20">
+        <v>0.09260327465570292</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.8</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>V4</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>-0.2787297834856938</v>
+      </c>
+      <c r="D21">
+        <v>0.1706084964705022</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.8</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>V5</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>0.1716000516462755</v>
+      </c>
+      <c r="D22">
+        <v>0.1011508222168174</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.8</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>V6</t>
         </is>
       </c>
-      <c r="C19">
-        <v>0.1716000516462755</v>
-      </c>
-      <c r="D19">
-        <v>0.1011508222168174</v>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>2.991635273407584E-09</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.8</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>0.05120757691971695</v>
+      </c>
+      <c r="D24">
+        <v>2.049959082822693E-09</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.8</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>0.2796759127138764</v>
+      </c>
+      <c r="D25">
+        <v>4.631119017095811E-10</v>
       </c>
     </row>
   </sheetData>
@@ -1287,7 +1505,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1383,19 +1601,19 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="G3">
-        <v>0.07444299905710433</v>
+        <v>0.001161416451474189</v>
       </c>
       <c r="H3">
-        <v>0.691658</v>
+        <v>0.51348</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1416,16 +1634,16 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>37</v>
       </c>
       <c r="G4">
-        <v>-0.05683273372172353</v>
+        <v>0.00379886380365966</v>
       </c>
       <c r="H4">
         <v>0.51348</v>
@@ -1446,22 +1664,22 @@
         <v>37</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>37</v>
       </c>
       <c r="G5">
-        <v>0.00379886380365966</v>
+        <v>-0.2537407657145344</v>
       </c>
       <c r="H5">
-        <v>0.51348</v>
+        <v>0.307403</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1482,19 +1700,19 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>37</v>
       </c>
       <c r="G6">
-        <v>-0.2537407657145344</v>
+        <v>0.1751093152128561</v>
       </c>
       <c r="H6">
-        <v>0.307403</v>
+        <v>1.116398</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1509,27 +1727,93 @@
         </is>
       </c>
       <c r="B7">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G7">
-        <v>0.1751093152128561</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>1.116398</v>
+        <v>6.168503</v>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>Confirmatória (meta-análise completa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>47</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>0.007758382978723405</v>
+      </c>
+      <c r="H8">
+        <v>6.168503</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Confirmatória (meta-análise completa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>47</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>43</v>
+      </c>
+      <c r="F9">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>0.03175936170212766</v>
+      </c>
+      <c r="H9">
+        <v>6.168503</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Confirmatória (meta-análise completa)</t>
         </is>
